--- a/data/trans_orig/IP26C-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP26C-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83908</t>
+          <t>83199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>94808</t>
+          <t>94906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>81660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>91536</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169387</t>
+          <t>168151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>184044</t>
+          <t>184099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15493</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29830</t>
+          <t>30419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5146</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72749</t>
+          <t>73479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>82485</t>
+          <t>82213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75535</t>
+          <t>75789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82690</t>
+          <t>82696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>152250</t>
+          <t>152077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>163672</t>
+          <t>163204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,86%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13117</t>
+          <t>12467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2585</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4609</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>52766</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61690</t>
+          <t>61524</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79639</t>
+          <t>80099</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90339</t>
+          <t>90701</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>135948</t>
+          <t>135474</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149665</t>
+          <t>149729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13789</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6387</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,47 +1921,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>3002</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>1055</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6939</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,64%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>5,85%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>3002</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6673</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>173809</t>
+          <t>174592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187432</t>
+          <t>187593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168488</t>
+          <t>167614</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>182858</t>
+          <t>182674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>347030</t>
+          <t>346370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>366732</t>
+          <t>365562</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,2%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30709</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33191</t>
+          <t>34396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53175</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3436</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>84432</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96076</t>
+          <t>96206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>114132</t>
+          <t>113639</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122539</t>
+          <t>122516</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>202477</t>
+          <t>202918</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216771</t>
+          <t>216840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>16282</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>22746</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>7878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>56962</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67122</t>
+          <t>67170</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62474</t>
+          <t>62454</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>69731</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122616</t>
+          <t>122778</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>135463</t>
+          <t>135570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23992</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>548000</t>
+          <t>548523</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>574877</t>
+          <t>574186</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>602524</t>
+          <t>603072</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>626217</t>
+          <t>626387</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1159440</t>
+          <t>1159754</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1195062</t>
+          <t>1195490</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>57919</t>
+          <t>58860</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84425</t>
+          <t>82631</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47217</t>
+          <t>47662</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>70664</t>
+          <t>70245</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>111865</t>
+          <t>111129</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>145851</t>
+          <t>144810</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,0%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10387</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6273</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16470</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>77383</t>
+          <t>77689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>85263</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75138</t>
+          <t>75548</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83990</t>
+          <t>84074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>155204</t>
+          <t>155824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>167720</t>
+          <t>167890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10696</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4463</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8800</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20423</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4475,7 +4475,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73416</t>
+          <t>72578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84145</t>
+          <t>83768</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80119</t>
+          <t>79919</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90582</t>
+          <t>90176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157559</t>
+          <t>157271</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171792</t>
+          <t>171776</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18381</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13813</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>27472</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>6773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71345</t>
+          <t>71648</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>81288</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71069</t>
+          <t>71498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80385</t>
+          <t>80463</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>146716</t>
+          <t>146578</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>159717</t>
+          <t>159924</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4869</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>14509</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14533</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12042</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>25181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>180236</t>
+          <t>180242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194361</t>
+          <t>193968</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>193110</t>
+          <t>193240</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207818</t>
+          <t>208152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>378835</t>
+          <t>379618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>398475</t>
+          <t>398595</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,96%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24500</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27681</t>
+          <t>27697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27785</t>
+          <t>28222</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>45987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6877</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6217</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>123462</t>
+          <t>122397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>136253</t>
+          <t>135950</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>115481</t>
+          <t>115337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128628</t>
+          <t>128185</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>241228</t>
+          <t>243488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>259982</t>
+          <t>261218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>19730</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9625</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21833</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40130</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>908</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>429</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9988</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38183</t>
+          <t>37542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47848</t>
+          <t>47439</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,49 +6454,49 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>60974</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>55023</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>66052</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>74,95%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
           <t>89,98%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>60974</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>54422</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>65653</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>83,06%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>74,13%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>150</t>
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>95976</t>
+          <t>96050</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110349</t>
+          <t>110456</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>13980</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>7358</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>18387</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29379</t>
+          <t>28937</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5766</t>
+          <t>5454</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>588215</t>
+          <t>585989</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>614348</t>
+          <t>612745</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>613342</t>
+          <t>614722</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>641126</t>
+          <t>642002</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1209926</t>
+          <t>1209033</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1248468</t>
+          <t>1247976</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>53392</t>
+          <t>54091</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78313</t>
+          <t>79973</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>59108</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>86505</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>118734</t>
+          <t>119346</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>155613</t>
+          <t>156682</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,82 +7136,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>7936</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>4439</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>13858</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>11925</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>6991</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>18210</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>7936</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>4492</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>13809</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>11925</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>7006</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>18535</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>69696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78059</t>
+          <t>78225</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85668</t>
+          <t>85662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95153</t>
+          <t>95008</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7640,7 +7640,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158584</t>
+          <t>158762</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>171316</t>
+          <t>171382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>11405</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>14135</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>9914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22565</t>
+          <t>21962</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -7816,7 +7816,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88963</t>
+          <t>89256</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98375</t>
+          <t>98864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>96140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>105977</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188840</t>
+          <t>189353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>202572</t>
+          <t>202890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>13739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11166</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24310</t>
+          <t>24007</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8272,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4749</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59237</t>
+          <t>59316</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60952</t>
+          <t>60026</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69925</t>
+          <t>70063</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>115429</t>
+          <t>115610</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127469</t>
+          <t>127488</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11265</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>18142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,28%</t>
         </is>
       </c>
     </row>
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7323</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>188839</t>
+          <t>188140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203567</t>
+          <t>203095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>181286</t>
+          <t>180536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>194577</t>
+          <t>193892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>374698</t>
+          <t>375274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>394300</t>
+          <t>395065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29312</t>
+          <t>28183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14284</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27575</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32174</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51202</t>
+          <t>50885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -9179,82 +9179,82 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>477</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5152</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1845</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9269,7 +9269,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119818</t>
+          <t>119368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129800</t>
+          <t>129955</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>123592</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>134759</t>
+          <t>134653</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>247908</t>
+          <t>248134</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262200</t>
+          <t>262685</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,58%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5217</t>
+          <t>5163</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15385</t>
+          <t>15409</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7450</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29462</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,47%</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9640,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9655,7 +9655,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56178</t>
+          <t>57554</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64695</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>109959</t>
+          <t>110380</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>121167</t>
+          <t>120962</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -10096,7 +10096,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>589150</t>
+          <t>589810</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>614720</t>
+          <t>613504</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>627354</t>
+          <t>626736</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>652290</t>
+          <t>651563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1223074</t>
+          <t>1225376</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1258814</t>
+          <t>1260212</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43884</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68176</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>48288</t>
+          <t>48656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>73159</t>
+          <t>72990</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>100612</t>
+          <t>99022</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>134002</t>
+          <t>133496</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12025</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10567,7 +10567,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5523</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>16319</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89602</t>
+          <t>89601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>98460</t>
+          <t>98610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109017</t>
+          <t>110857</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125056</t>
+          <t>125279</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203007</t>
+          <t>203042</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>220687</t>
+          <t>220639</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4662</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13670</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,7 +11139,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>9484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>23104</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>16523</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33741</t>
+          <t>33190</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>79982</t>
+          <t>79932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89823</t>
+          <t>89336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>80765</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90383</t>
+          <t>90187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164151</t>
+          <t>164170</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177546</t>
+          <t>177793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4858</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>14749</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15252</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12708</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26103</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>42732</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50074</t>
+          <t>50078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46553</t>
+          <t>47372</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57379</t>
+          <t>57648</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93405</t>
+          <t>92772</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106067</t>
+          <t>105639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1358</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20844</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>192317</t>
+          <t>192371</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207941</t>
+          <t>207669</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>195697</t>
+          <t>196365</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>209314</t>
+          <t>208794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392785</t>
+          <t>393889</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>413329</t>
+          <t>412808</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>23659</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20603</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21030</t>
+          <t>21258</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40034</t>
+          <t>39226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12625,7 +12625,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>861</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6806</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>96247</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108627</t>
+          <t>108802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137724</t>
+          <t>137559</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153010</t>
+          <t>152468</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>239122</t>
+          <t>238973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258455</t>
+          <t>259069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9607</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>24893</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22220</t>
+          <t>21338</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41299</t>
+          <t>40806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>465</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -13291,12 +13291,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>61875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67458</t>
+          <t>67305</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>51626</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64724</t>
+          <t>64450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116056</t>
+          <t>115612</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>130299</t>
+          <t>130045</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10414</t>
+          <t>10511</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24546</t>
+          <t>25061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -13557,7 +13557,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1987</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13592,7 +13592,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1856</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>582907</t>
+          <t>584230</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>609384</t>
+          <t>609086</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>649556</t>
+          <t>651835</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>681020</t>
+          <t>682292</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1243059</t>
+          <t>1242680</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1282522</t>
+          <t>1282875</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43295</t>
+          <t>43325</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68648</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>62816</t>
+          <t>62019</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93429</t>
+          <t>92037</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113873</t>
+          <t>113557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>153155</t>
+          <t>153905</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,7 +13988,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15731</t>
+          <t>15694</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,7 +14058,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
